--- a/data/trans_dic/P1429-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1429-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,48</t>
+          <t>0,56; 2,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,84</t>
+          <t>0,57; 1,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,23</t>
+          <t>2,4; 5,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,18</t>
+          <t>1,64; 4,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,74</t>
+          <t>2,54; 5,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,26</t>
+          <t>4,35; 7,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,46</t>
+          <t>1,79; 3,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,26</t>
+          <t>0,97; 2,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,18</t>
+          <t>1,39; 3,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,38</t>
+          <t>2,66; 4,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,22</t>
+          <t>0,66; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,94</t>
+          <t>0,09; 0,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,22</t>
+          <t>0,41; 1,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,21</t>
+          <t>2,6; 5,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,15</t>
+          <t>2,53; 4,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,74</t>
+          <t>2,46; 5,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,22</t>
+          <t>3,45; 5,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,4</t>
+          <t>1,91; 3,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,6</t>
+          <t>1,28; 2,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,64</t>
+          <t>1,36; 2,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,81</t>
+          <t>2,02; 3,09</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,11</t>
+          <t>0,11; 1,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,3</t>
+          <t>0,23; 1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,79</t>
+          <t>4,17; 7,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,93</t>
+          <t>2,37; 5,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,77</t>
+          <t>2,6; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,91</t>
+          <t>3,44; 5,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,09</t>
+          <t>2,23; 4,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,67</t>
+          <t>1,23; 2,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,03</t>
+          <t>1,47; 3,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,94</t>
+          <t>2,01; 3,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,0</t>
+          <t>0,1; 0,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,89</t>
+          <t>0,34; 2,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,68</t>
+          <t>3,17; 5,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,48</t>
+          <t>4,41; 7,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,94</t>
+          <t>1,83; 3,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,74</t>
+          <t>4,04; 6,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,49</t>
+          <t>2,04; 3,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,0</t>
+          <t>2,45; 4,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,3</t>
+          <t>1,14; 2,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,75</t>
+          <t>2,5; 3,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,47</t>
+          <t>0,74; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,44</t>
+          <t>0,06; 0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,59</t>
+          <t>0,19; 0,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,32</t>
+          <t>0,57; 1,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,0</t>
+          <t>3,6; 5,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,8</t>
+          <t>3,36; 4,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,17</t>
+          <t>2,82; 4,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,01</t>
+          <t>4,21; 5,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,12</t>
+          <t>2,33; 3,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,5</t>
+          <t>1,78; 2,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,61; 2,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,0</t>
+          <t>2,54; 3,19</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45499</t>
+          <t>47273</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3989; 17207</t>
+          <t>3863; 17504</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7288</t>
+          <t>0; 7210</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7061</t>
+          <t>0; 6535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3482; 11698</t>
+          <t>3927; 13167</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16544; 36026</t>
+          <t>16519; 37231</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10791; 29154</t>
+          <t>11433; 29729</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17824; 38612</t>
+          <t>17097; 37895</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30856; 49011</t>
+          <t>31823; 52003</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24517; 47783</t>
+          <t>24770; 48572</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12614; 31676</t>
+          <t>13641; 34471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19178; 42845</t>
+          <t>18760; 42032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36738; 57388</t>
+          <t>37840; 60037</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48441</t>
+          <t>53765</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7155; 21398</t>
+          <t>6300; 21481</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1863,52 +1863,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1183; 9589</t>
+          <t>917; 9860</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3115; 14591</t>
+          <t>4279; 15736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26251; 50435</t>
+          <t>25212; 50129</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25943; 53019</t>
+          <t>26065; 50196</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23917; 49462</t>
+          <t>25688; 52399</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32099; 49778</t>
+          <t>36716; 57120</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37163; 65552</t>
+          <t>36947; 64251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27018; 53196</t>
+          <t>26191; 49104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27891; 54626</t>
+          <t>28100; 55298</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32366; 60219</t>
+          <t>42639; 65268</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>41046</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>751; 7523</t>
+          <t>754; 7233</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 13492</t>
+          <t>0; 13171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7556</t>
+          <t>0; 7863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1484; 9129</t>
+          <t>1833; 11183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28162; 53262</t>
+          <t>28496; 52358</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17370; 38296</t>
+          <t>18415; 39354</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20921; 45327</t>
+          <t>20434; 43999</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15027; 45647</t>
+          <t>27737; 46731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30274; 55766</t>
+          <t>30448; 57484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18434; 40933</t>
+          <t>18851; 42897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21212; 46822</t>
+          <t>22711; 48037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22437; 47929</t>
+          <t>32215; 52570</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>55148</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59363</t>
+          <t>64197</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4773; 16284</t>
+          <t>4782; 16261</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6178</t>
+          <t>0; 8021</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1005; 9378</t>
+          <t>926; 9033</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3945; 26724</t>
+          <t>3388; 22842</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33258; 58942</t>
+          <t>32923; 59741</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48259; 78659</t>
+          <t>46434; 80479</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19146; 41074</t>
+          <t>19099; 41641</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37389; 62489</t>
+          <t>44995; 68583</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40302; 69209</t>
+          <t>40389; 68175</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48777; 79964</t>
+          <t>49024; 79928</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22254; 45638</t>
+          <t>22645; 47185</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47739; 75605</t>
+          <t>52502; 82246</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>206281</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24797; 48276</t>
+          <t>24124; 46684</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2057; 15112</t>
+          <t>2053; 16314</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6004; 20052</t>
+          <t>6567; 20549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19725; 45696</t>
+          <t>20019; 43297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>121146; 169092</t>
+          <t>121541; 169876</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>119238; 170426</t>
+          <t>119540; 170831</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>101099; 147982</t>
+          <t>100010; 146917</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>133684; 182674</t>
+          <t>156533; 197422</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153714; 207773</t>
+          <t>155055; 206130</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123147; 174630</t>
+          <t>124345; 175054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112228; 159314</t>
+          <t>111519; 158527</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>160015; 212931</t>
+          <t>183894; 231336</t>
         </is>
       </c>
     </row>
